--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.84.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.84.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -887,7 +887,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.84.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.84.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: served with subpo Ã¦ ena out of the jurisdiction</t>
+          <t>L47: stray/suspicious non-ASCII glyph(s): U+8FD0 CJK UNIFIED IDEOGRAPH-8FD0 | isolated marker/symbol line :: 运</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: is to be set down toâ€™ be heard ; and the Court, if it so, made,</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L25: isolated marker/symbol line :: 77</t>
@@ -626,7 +630,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -636,7 +640,11 @@
       </c>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • by himself or his own solicitor, or upon notice served up-</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -657,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -680,12 +688,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: è¿�</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 、 心</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ by himself or his own solicitor, or upon notice served up-</t>
+          <t>L44: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • by himself or his own solicitor, or upon notice served up-</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -745,14 +753,10 @@
           <t>L23: suspicious token(s): may4 (letter/digit mix) | localized OCR phrase divergence vs other OCR: "circumstance" vs "circumstances of the case may4" :: further notice as under the circumstances of the case may4</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ã€� å¿ƒ</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: 550.â€�</t>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -764,7 +768,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L61: symbol-only separator/garbage line :: 550.”</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -786,12 +790,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -808,24 +812,20 @@
           <t>L41: suspicious token(s): 80lute (letter/digit mix) :: defendant, who has appeared at the hearing and waived all 80lute</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: è¿�</t>
-        </is>
-      </c>
-      <c r="O5" s="1" t="inlineStr"/>
+          <t>L47: stray/suspicious non-ASCII glyph(s): U+8FD0 CJK UNIFIED IDEOGRAPH-8FD0 | isolated marker/symbol line :: 运</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -959,7 +959,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 、 心</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: .</t>
+          <t>L89: isolated marker/symbol line :: 、</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1045,7 +1045,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: b</t>
+          <t>L90: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1088,7 +1088,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L97: isolated marker/symbol line :: 01</t>
+          <t>L91: isolated marker/symbol line :: b</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1131,7 +1131,7 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L102: isolated marker/symbol line :: 1</t>
+          <t>L97: isolated marker/symbol line :: 01</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: e</t>
+          <t>L102: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr"/>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1217,7 +1217,7 @@
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L136: isolated marker/symbol line :: 2</t>
+          <t>L108: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr"/>
@@ -1258,7 +1258,11 @@
       <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
-      <c r="N15" s="1" t="inlineStr"/>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t>L136: isolated marker/symbol line :: 2</t>
+        </is>
+      </c>
       <c r="O15" s="1" t="inlineStr"/>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr"/>
